--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_depmenores_a_2018_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_depmenores_a_2018_magallanes.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:49</t>
+    <t xml:space="preserve">2026-09-24 00:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -544,10 +544,10 @@
         <v>5</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -566,7 +566,7 @@
         <v>-0.11</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G3" s="2"/>
     </row>
@@ -582,10 +582,10 @@
         <v>5</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G4" s="2"/>
     </row>
@@ -604,7 +604,7 @@
         <v>-0.05</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G5" s="2"/>
     </row>
@@ -623,7 +623,7 @@
         <v>-0.04</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G6" s="2"/>
     </row>
@@ -635,19 +635,19 @@
         <v>14</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.42</v>
+        <v>0.03</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.26</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="8">
@@ -658,19 +658,19 @@
         <v>14</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.34</v>
+        <v>0.18</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.18</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9">
@@ -681,19 +681,19 @@
         <v>14</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.4</v>
+        <v>0.23</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.17</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="10">
@@ -704,19 +704,19 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.12</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0.15</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="11">
@@ -727,19 +727,19 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.12</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="12">
@@ -750,19 +750,19 @@
         <v>14</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>-0.56</v>
+        <v>-0.29</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-0.58</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="13">
@@ -773,19 +773,19 @@
         <v>14</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-0.72</v>
+        <v>-0.43</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.84</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="14">
@@ -802,10 +802,10 @@
         <v>7</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0.94</v>
@@ -828,7 +828,7 @@
         <v>-0.06</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0.53</v>
@@ -842,19 +842,19 @@
         <v>14</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.32</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>-0.38</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.12</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="17">
@@ -865,19 +865,19 @@
         <v>14</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.2</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.1</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="18">
@@ -895,7 +895,7 @@
         <v>-0.22</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G18" s="2"/>
     </row>
